--- a/SbslFileTransformer/EscalationUploads/sample_escalations.xlsx
+++ b/SbslFileTransformer/EscalationUploads/sample_escalations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\SBSL\SbslFileTransformer\SbslFileTransformer\EscalationUploads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yida\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E38DC4E-3D41-4BFA-B3A6-8996AD1B7D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C6AC11-E16C-48BF-8BF9-31C21E763285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B00D029B-F366-4782-9E65-368DA9FBDC3C}"/>
+    <workbookView xWindow="300" yWindow="8010" windowWidth="38190" windowHeight="12990" xr2:uid="{B00D029B-F366-4782-9E65-368DA9FBDC3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -78,6 +76,9 @@
   </si>
   <si>
     <t>test@email.com,test2@company.com</t>
+  </si>
+  <si>
+    <t>IsManagerReport</t>
   </si>
 </sst>
 </file>
@@ -440,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1FF69F-7127-4CBD-9E48-93818F46A7EC}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
@@ -449,9 +450,10 @@
     <col min="4" max="4" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -471,10 +473,13 @@
         <v>8</v>
       </c>
       <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -496,8 +501,11 @@
       <c r="G2" t="b">
         <v>1</v>
       </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -519,8 +527,11 @@
       <c r="G3" t="b">
         <v>1</v>
       </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -540,6 +551,9 @@
         <v>13</v>
       </c>
       <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="b">
         <v>1</v>
       </c>
     </row>
